--- a/artfynd/A 47107-2021 artfynd.xlsx
+++ b/artfynd/A 47107-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47107-2021 artfynd.xlsx
+++ b/artfynd/A 47107-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>109726179</v>
       </c>
       <c r="B2" t="n">
-        <v>57063</v>
+        <v>57064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2021 artfynd.xlsx
+++ b/artfynd/A 47107-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>109726179</v>
       </c>
       <c r="B2" t="n">
-        <v>57064</v>
+        <v>57068</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2021 artfynd.xlsx
+++ b/artfynd/A 47107-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>109726179</v>
       </c>
       <c r="B2" t="n">
-        <v>57068</v>
+        <v>57069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2021 artfynd.xlsx
+++ b/artfynd/A 47107-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,15 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109726179</v>
+        <v>97220218</v>
       </c>
       <c r="B2" t="n">
-        <v>57069</v>
+        <v>95511</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,47 +691,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102954</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kohagen, Srm</t>
+          <t>Nynäs NR, Kohagen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>636033</v>
+        <v>636036.3348157634</v>
       </c>
       <c r="R2" t="n">
-        <v>6520456</v>
+        <v>6520304.180386545</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2021-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2021-11-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,6 +773,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,6 +789,123 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>109726179</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57069</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kohagen, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>636033</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6520456</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Stephan Gäfvert</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Stephan Gäfvert</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47107-2021 artfynd.xlsx
+++ b/artfynd/A 47107-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97220218</v>
+        <v>97217163</v>
       </c>
       <c r="B2" t="n">
-        <v>95511</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nynäs NR, Kohagen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>636036.3348157634</v>
+        <v>635967</v>
       </c>
       <c r="R2" t="n">
-        <v>6520304.180386545</v>
+        <v>6520164</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109726179</v>
+        <v>54116763</v>
       </c>
       <c r="B3" t="n">
-        <v>57069</v>
+        <v>97811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,47 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>2604</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Pfeiff.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kohagen, Srm</t>
+          <t>Bergkant i fd skogsbete västerom kalkberget, Nynäs NR, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>636033</v>
+        <v>636200</v>
       </c>
       <c r="R3" t="n">
-        <v>6520456</v>
+        <v>6520424</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +852,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:47</t>
+          <t>2015-05-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:47</t>
+          <t>2015-05-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På bergvägg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,15 +877,351 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Markus Forsberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>96845203</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91893</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nynäs NR, Kohagen, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>636182</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6520466</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Stephan Gäfvert</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Stephan Gäfvert</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>109726147</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57364</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kohagen, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>636033</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6520456</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Stephan Gäfvert</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Stephan Gäfvert</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>97220218</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nynäs NR, Kohagen, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>636037</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6520304</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-11-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-11-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Stephan Gäfvert</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Stephan Gäfvert</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47107-2021 artfynd.xlsx
+++ b/artfynd/A 47107-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97217163</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54116763</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96845203</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109726147</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,8 +1247,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97220218</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>